--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -761,10 +761,10 @@
         <v>0.8303571428571429</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8613861386138614</v>
+        <v>0.8811881188118812</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8428637555093785</v>
+        <v>0.8478142505588835</v>
       </c>
     </row>
     <row r="15">
@@ -783,10 +783,10 @@
         <v>0.525</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5608614232209738</v>
+        <v>0.5720973782771536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5155806155455032</v>
+        <v>0.5183896043095482</v>
       </c>
     </row>
     <row r="16">
@@ -805,10 +805,10 @@
         <v>0.5008210180623973</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5730676328502415</v>
+        <v>0.592741935483871</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4967098918825062</v>
+        <v>0.5016284675409136</v>
       </c>
     </row>
     <row r="17">
@@ -827,10 +827,10 @@
         <v>0.7615528970208773</v>
       </c>
       <c r="E17" t="n">
-        <v>0.840543836992395</v>
+        <v>0.8540402427339507</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7931643366961887</v>
+        <v>0.7965384381315775</v>
       </c>
     </row>
     <row r="18">
@@ -843,16 +843,16 @@
         <v>0.7488636363636364</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5352564102564102</v>
+        <v>0.5663919413919413</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7168478260869566</v>
+        <v>0.7206521739130436</v>
       </c>
       <c r="E18" t="n">
-        <v>0.691947565543071</v>
+        <v>0.7181647940074906</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6732288595625185</v>
+        <v>0.688518136419028</v>
       </c>
     </row>
     <row r="19">
@@ -878,12 +878,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[85, 4], [10, 2]]</t>
+          <t>[[87, 2], [10, 2]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[86, 2], [14, 1]]</t>
+          <t>[[87, 2], [14, 1]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8428637555093785</v>
+        <v>0.8478142505588835</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01187172943465143</v>
+        <v>0.01994617996516229</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5155806155455032</v>
+        <v>0.5183896043095482</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0304518107928208</v>
+        <v>0.03471844746191719</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4967098918825062</v>
+        <v>0.5016284675409136</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04766826501270191</v>
+        <v>0.05564156091406287</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7931643366961887</v>
+        <v>0.7965384381315775</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0290893236960429</v>
+        <v>0.03464201083218069</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6732288595625185</v>
+        <v>0.688518136419028</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0821736278004202</v>
+        <v>0.07153304751510504</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[86, 2], [14, 1]]</t>
+          <t>[[87, 2], [14, 1]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -616,13 +616,13 @@
         <v>0.8762886597938144</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8491977468547718</v>
+        <v>0.8519160990471339</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.8545454545454545</v>
       </c>
       <c r="C9" t="n">
-        <v>0.766025641025641</v>
+        <v>0.7335164835164836</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8304347826086957</v>
+        <v>0.8054347826086956</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8019662921348314</v>
+        <v>0.7411048689138577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8132430425786557</v>
+        <v>0.7836503973961229</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.8106934001670844</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7495697074010327</v>
+        <v>0.7335164835164836</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7268292682926829</v>
+        <v>0.7123780174627632</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7170868347338936</v>
+        <v>0.7097701149425287</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7510448026486733</v>
+        <v>0.741589504022215</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8992708307986795</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8799616729066486</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D11" t="n">
-        <v>0.808362369337979</v>
+        <v>0.7998752659769609</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8601658485176249</v>
+        <v>0.869693865938318</v>
       </c>
       <c r="F11" t="n">
-        <v>0.861940180390233</v>
+        <v>0.8612821556269432</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.9</v>
       </c>
       <c r="C12" t="n">
-        <v>0.858058608058608</v>
+        <v>0.8489010989010989</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8782608695652174</v>
+        <v>0.8864130434782609</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8848314606741573</v>
+        <v>0.8876404494382022</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8802877345744956</v>
+        <v>0.8807386479543906</v>
       </c>
     </row>
     <row r="13">
@@ -726,22 +726,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[77, 7], [5, 8]]</t>
+          <t>[[78, 6], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[70, 22], [2, 18]]</t>
+          <t>[[70, 22], [3, 17]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[76, 13], [3, 9]]</t>
+          <t>[[80, 9], [5, 7]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[76, 12], [3, 12]]</t>
+          <t>[[77, 11], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8491977468547718</v>
+        <v>0.8519160990471339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04110527397176385</v>
+        <v>0.0448133886962659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8132430425786557</v>
+        <v>0.7836503973961229</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0330079280988923</v>
+        <v>0.04955855093226364</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7510448026486733</v>
+        <v>0.741589504022215</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03639940514950198</v>
+        <v>0.04094602114645678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.861940180390233</v>
+        <v>0.8612821556269432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03388245026256977</v>
+        <v>0.0371143421585969</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8802877345744956</v>
+        <v>0.8807386479543906</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01506204752431967</v>
+        <v>0.01913415036413246</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[76, 12], [3, 12]]</t>
+          <t>[[77, 11], [4, 11]]</t>
         </is>
       </c>
     </row>
